--- a/images/citations.xlsx
+++ b/images/citations.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacques.klein/jacquesklein2302.github.io/images/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBBD65C9-F639-D74F-B3E6-3EBAAB5D77B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF23A66-7E00-6D4B-84EC-A5D33163F350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="1620" windowWidth="33660" windowHeight="20360" xr2:uid="{ACB19145-8E22-7D4E-9954-B957022569C7}"/>
   </bookViews>
@@ -910,6 +910,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -917,7 +918,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1749,6 +1749,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1756,7 +1757,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2333,6 +2333,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2340,7 +2341,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4418,7 +4418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4CD39B4-C474-484D-A525-0FA885BAEB22}">
-  <dimension ref="A4:D183"/>
+  <dimension ref="A4:D191"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -5455,39 +5455,85 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>46082</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>46113</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>46143</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <v>46174</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>46204</v>
       </c>
-    </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B181">
+        <v>20033</v>
+      </c>
+      <c r="C181">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>46235</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>46266</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A184" s="1">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A185" s="1">
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A186" s="1">
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A187" s="1">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A188" s="1">
+        <v>46419</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A189" s="1">
+        <v>46447</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A190" s="1">
+        <v>46478</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A191" s="1">
+        <v>46508</v>
       </c>
     </row>
   </sheetData>

--- a/images/citations.xlsx
+++ b/images/citations.xlsx
@@ -8,17 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacques.klein/jacquesklein2302.github.io/images/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF23A66-7E00-6D4B-84EC-A5D33163F350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E84DC717-B35F-5F44-8D75-97DE5A18A3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="1620" windowWidth="33660" windowHeight="20360" xr2:uid="{ACB19145-8E22-7D4E-9954-B957022569C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -203,10 +214,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$5:$A$174</c:f>
+              <c:f>Sheet1!$A$5:$A$181</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yy</c:formatCode>
-                <c:ptCount val="170"/>
+                <c:ptCount val="177"/>
                 <c:pt idx="0">
                   <c:v>40848</c:v>
                 </c:pt>
@@ -716,16 +727,37 @@
                 </c:pt>
                 <c:pt idx="169">
                   <c:v>45992</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>46023</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>46054</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>46082</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>46143</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>46174</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>46204</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$5:$B$174</c:f>
+              <c:f>Sheet1!$B$5:$B$181</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="170"/>
+                <c:ptCount val="177"/>
                 <c:pt idx="0">
                   <c:v>329</c:v>
                 </c:pt>
@@ -770,6 +802,9 @@
                 </c:pt>
                 <c:pt idx="168">
                   <c:v>18300</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>20033</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1042,10 +1077,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$5:$A$174</c:f>
+              <c:f>Sheet1!$A$5:$A$181</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yy</c:formatCode>
-                <c:ptCount val="170"/>
+                <c:ptCount val="177"/>
                 <c:pt idx="0">
                   <c:v>40848</c:v>
                 </c:pt>
@@ -1555,16 +1590,37 @@
                 </c:pt>
                 <c:pt idx="169">
                   <c:v>45992</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>46023</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>46054</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>46082</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>46143</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>46174</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>46204</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$5:$C$174</c:f>
+              <c:f>Sheet1!$C$5:$C$181</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="170"/>
+                <c:ptCount val="177"/>
                 <c:pt idx="0">
                   <c:v>9</c:v>
                 </c:pt>
@@ -1609,6 +1665,9 @@
                 </c:pt>
                 <c:pt idx="168">
                   <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>65</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
